--- a/results/0916-all/北疆农牧林区/tech_selected_summary.xlsx
+++ b/results/0916-all/北疆农牧林区/tech_selected_summary.xlsx
@@ -151,286 +151,286 @@
     <t>昭苏县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>技术70</t>
-  </si>
-  <si>
-    <t>技术71</t>
-  </si>
-  <si>
-    <t>技术72</t>
-  </si>
-  <si>
-    <t>技术73</t>
-  </si>
-  <si>
-    <t>技术74</t>
-  </si>
-  <si>
-    <t>技术75</t>
-  </si>
-  <si>
-    <t>技术76</t>
-  </si>
-  <si>
-    <t>技术77</t>
-  </si>
-  <si>
-    <t>技术78</t>
-  </si>
-  <si>
-    <t>技术79</t>
-  </si>
-  <si>
-    <t>技术80</t>
-  </si>
-  <si>
-    <t>技术81</t>
-  </si>
-  <si>
-    <t>技术82</t>
-  </si>
-  <si>
-    <t>技术83</t>
-  </si>
-  <si>
-    <t>技术84</t>
-  </si>
-  <si>
-    <t>技术85</t>
-  </si>
-  <si>
-    <t>技术86</t>
-  </si>
-  <si>
-    <t>技术87</t>
-  </si>
-  <si>
-    <t>技术88</t>
-  </si>
-  <si>
-    <t>技术89</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Tech70</t>
+  </si>
+  <si>
+    <t>Tech71</t>
+  </si>
+  <si>
+    <t>Tech72</t>
+  </si>
+  <si>
+    <t>Tech73</t>
+  </si>
+  <si>
+    <t>Tech74</t>
+  </si>
+  <si>
+    <t>Tech75</t>
+  </si>
+  <si>
+    <t>Tech76</t>
+  </si>
+  <si>
+    <t>Tech77</t>
+  </si>
+  <si>
+    <t>Tech78</t>
+  </si>
+  <si>
+    <t>Tech79</t>
+  </si>
+  <si>
+    <t>Tech80</t>
+  </si>
+  <si>
+    <t>Tech81</t>
+  </si>
+  <si>
+    <t>Tech82</t>
+  </si>
+  <si>
+    <t>Tech83</t>
+  </si>
+  <si>
+    <t>Tech84</t>
+  </si>
+  <si>
+    <t>Tech85</t>
+  </si>
+  <si>
+    <t>Tech86</t>
+  </si>
+  <si>
+    <t>Tech87</t>
+  </si>
+  <si>
+    <t>Tech88</t>
+  </si>
+  <si>
+    <t>Tech89</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 221118.66</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>221118.66</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Low protein diet_Pig</t>
@@ -526,22 +526,22 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 211347870.84</t>
+    <t>211347870.84</t>
   </si>
   <si>
     <t>Chemical amendments_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 12565727.67</t>
+    <t>12565727.67</t>
   </si>
   <si>
     <t>EEF(NI)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 1619154.98</t>
-  </si>
-  <si>
-    <t>总经济成本: 72659873.87</t>
+    <t>1619154.98</t>
+  </si>
+  <si>
+    <t>72659873.87</t>
   </si>
   <si>
     <t>Low protein diet_dairy</t>
@@ -703,7 +703,7 @@
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 1236925239.33</t>
+    <t>1236925239.33</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -721,25 +721,25 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 398973484.49</t>
+    <t>398973484.49</t>
   </si>
   <si>
     <t>Yucca extract_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 212892031.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 49975386.37</t>
+    <t>212892031.59</t>
+  </si>
+  <si>
+    <t>49975386.37</t>
   </si>
   <si>
     <t>EEF(NI)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 856737348.38</t>
-  </si>
-  <si>
-    <t>总经济成本: 143636902.99</t>
+    <t>856737348.38</t>
+  </si>
+  <si>
+    <t>143636902.99</t>
   </si>
 </sst>
 </file>
